--- a/Outputs/Scenarios/PtX_demand_MT_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_MT_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.000321432175639902</v>
+        <v>0.0003484563351089362</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>7.229842503574039e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.000642864351279804</v>
+        <v>0.0005783874002859231</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000107144058546634</v>
+        <v>7.229842503574039e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.001734884400097794</v>
+        <v>0.001880743452929848</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.0003902204547396131</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003469768800195588</v>
+        <v>0.003121763637916905</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0005782948000325979</v>
+        <v>0.0003902204547396131</v>
       </c>
     </row>
     <row r="43">
